--- a/Bauteillisten/Bestellliste_DigiKey_V6.xlsx
+++ b/Bauteillisten/Bestellliste_DigiKey_V6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\Bauteillisten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janne\Documents\GitHub\active-balancing\Bauteillisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1CAAC36-6A24-46EE-A49B-D5A8B620BCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9508DF-1D43-4B68-A33B-C6C63AD00F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -536,7 +536,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -594,12 +594,12 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -915,34 +915,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="6.81640625" customWidth="1"/>
-    <col min="3" max="3" width="37.81640625" customWidth="1"/>
-    <col min="4" max="4" width="29.6328125" customWidth="1"/>
-    <col min="5" max="5" width="43.1796875" customWidth="1"/>
-    <col min="6" max="6" width="18.90625" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" customWidth="1"/>
-    <col min="8" max="8" width="21.54296875" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="1" max="2" width="6.77734375" customWidth="1"/>
+    <col min="3" max="3" width="37.77734375" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" customWidth="1"/>
+    <col min="5" max="5" width="43.21875" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -974,7 +974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12">
       <c r="A24" s="5">
         <v>22</v>
       </c>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12">
       <c r="A25" s="5">
         <v>23</v>
       </c>
@@ -1706,11 +1706,11 @@
       <c r="J25" s="7">
         <v>1.22</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="9" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -1869,11 +1869,11 @@
       <c r="K30" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="L30" s="10" t="s">
+      <c r="L30" s="8" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -1904,11 +1904,11 @@
       <c r="K31" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="L31" s="8" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -2003,11 +2003,11 @@
       <c r="K34" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="L34" s="10">
+      <c r="L34" s="8">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12">
       <c r="A35" s="5">
         <v>33</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -2357,11 +2357,11 @@
       <c r="K45" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="L45" s="10" t="s">
+      <c r="L45" s="8" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12">
       <c r="A52" s="2">
         <v>48</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12">
       <c r="A53" s="2">
         <v>49</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12">
       <c r="A54" s="2">
         <v>50</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12">
       <c r="A55" s="2">
         <v>51</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12">
       <c r="A56" s="2">
         <v>52</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12">
       <c r="A57" s="2">
         <v>53</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12">
       <c r="A58" s="2">
         <v>54</v>
       </c>
